--- a/docs/collections/asia/metadata/data.xlsx
+++ b/docs/collections/asia/metadata/data.xlsx
@@ -10914,9 +10914,7 @@
       <c r="F25" t="s">
         <v>332</v>
       </c>
-      <c r="G25" t="s">
-        <v>333</v>
-      </c>
+      <c r="G25" t="s"/>
       <c r="H25" t="s">
         <v>333</v>
       </c>
@@ -11032,9 +11030,7 @@
       <c r="F26" t="s">
         <v>332</v>
       </c>
-      <c r="G26" t="s">
-        <v>333</v>
-      </c>
+      <c r="G26" t="s"/>
       <c r="H26" t="s">
         <v>333</v>
       </c>
@@ -11150,9 +11146,7 @@
       <c r="F27" t="s">
         <v>332</v>
       </c>
-      <c r="G27" t="s">
-        <v>362</v>
-      </c>
+      <c r="G27" t="s"/>
       <c r="H27" t="s">
         <v>362</v>
       </c>
@@ -11268,9 +11262,7 @@
       <c r="F28" t="s">
         <v>332</v>
       </c>
-      <c r="G28" t="s">
-        <v>374</v>
-      </c>
+      <c r="G28" t="s"/>
       <c r="H28" t="s">
         <v>374</v>
       </c>

--- a/docs/collections/asia/metadata/data.xlsx
+++ b/docs/collections/asia/metadata/data.xlsx
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>11668</v>
+        <v>11509</v>
       </c>
     </row>
     <row r="3">
@@ -8451,7 +8451,7 @@
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr"/>
       <c r="BJ40" t="n">
-        <v>226</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
